--- a/PMS_Report_DPR-385_All_Time.xlsx
+++ b/PMS_Report_DPR-385_All_Time.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26 12:06</t>
+          <t>2026-07-26 12:18</t>
         </is>
       </c>
     </row>

--- a/PMS_Report_DPR-385_All_Time.xlsx
+++ b/PMS_Report_DPR-385_All_Time.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26 12:18</t>
+          <t>2026-07-26 16:32</t>
         </is>
       </c>
     </row>

--- a/PMS_Report_DPR-385_All_Time.xlsx
+++ b/PMS_Report_DPR-385_All_Time.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26 16:32</t>
+          <t>2026-07-26 16:43</t>
         </is>
       </c>
     </row>
